--- a/www/download/COUNTRY.USA.rpA2.xlsx
+++ b/www/download/COUNTRY.USA.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>Estados Unidos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.0000000020846</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>0.999999998842423</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.999999995079282</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>0.99999999562278</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.608</t>
+          <t>0.999999996660455</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>1.00000000300325</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.748</t>
+          <t>0.9999999982869</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.736</t>
+          <t>0.999999996719295</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>0.999999999213553</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.815</t>
+          <t>1.00000000130348</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.000000002288</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0.999999996442966</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2.112</t>
+          <t>1.00000000279833</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2.255</t>
+          <t>1.00000000415777</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2.308</t>
+          <t>0.999999995453474</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>133.979</t>
+          <t>2.27836660316184</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>136.023</t>
+          <t>2.30697795650734</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>138.548</t>
+          <t>2.27729920587563</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>141.887</t>
+          <t>2.08944685555994</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>144.534</t>
+          <t>2.02029402837317</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>147.717</t>
+          <t>1.65448115484279</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>146.818</t>
+          <t>1.5094052576737</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>145.399</t>
+          <t>1.44853796094504</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>145.189</t>
+          <t>1.37735871491173</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>146.865</t>
+          <t>1.29828827456722</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>148.903</t>
+          <t>1.30282117979391</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>151.319</t>
+          <t>1.32127496377299</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>152.567</t>
+          <t>1.49627492930713</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>151.743</t>
+          <t>1.57814536578502</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>145.345</t>
+          <t>1.57931288149522</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>123.518</t>
+          <t>1.16809604824328</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>125.56</t>
+          <t>1.18642926504756</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>128.056</t>
+          <t>1.22304763704094</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>131.603</t>
+          <t>1.11281733038523</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>134.466</t>
+          <t>1.04318943518884</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>137.538</t>
+          <t>0.912662009229841</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>136.742</t>
+          <t>0.822760906090115</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>135.486</t>
+          <t>0.753150347333491</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>134.951</t>
+          <t>0.707686473705158</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>136.496</t>
+          <t>0.697637582179089</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>139.146</t>
+          <t>0.695273326713401</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>141.466</t>
+          <t>0.745424041741351</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>142.838</t>
+          <t>0.811994088093919</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>142.317</t>
+          <t>0.887104280365055</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>136.175</t>
+          <t>0.907384080755075</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>242776.093</t>
+          <t>0.226044041697404</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>246938.593</t>
+          <t>0.241952416964189</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>253228.389</t>
+          <t>0.188246527454046</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>258805.731</t>
+          <t>0.218111589049399</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>263627.014</t>
+          <t>0.212325180153003</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>269026.187</t>
+          <t>0.117623408827814</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>266094.82</t>
+          <t>0.0726776244118204</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>262808.915</t>
+          <t>0.0516913201246401</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>261841.126</t>
+          <t>0.0216597755677737</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>264757.46</t>
+          <t>0.0267948359760015</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>267643.044</t>
+          <t>0.0463330647941878</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>273342.068</t>
+          <t>0.0614193412145949</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>275293.945</t>
+          <t>0.0980623839153414</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>271688.068</t>
+          <t>0.168144882423205</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>259200.648</t>
+          <t>0.161769814993923</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>222377.918</t>
+          <t>688904487076.029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>226311.857</t>
+          <t>696677023483.492</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>232419.816</t>
+          <t>704925971602.619</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>238264.033</t>
+          <t>721066183468.815</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>243345.874</t>
+          <t>741618570785.513</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>248180.096</t>
+          <t>783652956182.161</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>245372.044</t>
+          <t>756836349884.297</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>242440.736</t>
+          <t>732297767804.518</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>240823.365</t>
+          <t>737335527221.888</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>243449.993</t>
+          <t>779488087745.246</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>247601.002</t>
+          <t>806016860198.5</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>252739.809</t>
+          <t>827003984510.719</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>254926.998</t>
+          <t>811145797553.009</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>252853.572</t>
+          <t>813774404940.18</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>240900.197</t>
+          <t>706030254609.161</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>290406385543.561</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>293950143661.481</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>301287615183.409</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>326187496097.005</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>342755749115.23</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>384745139633.272</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>34.77</t>
+          <t>400497841957.687</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>408819562454.388</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>419320529434.201</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>35.96</t>
+          <t>433843883936.475</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>441648054953.128</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>36.92</t>
+          <t>444016965450.416</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>426908083088.703</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>410499950071.402</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>37.92</t>
+          <t>391462669977.231</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>58.44</t>
+          <t>2715877.64093158</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.03</t>
+          <t>2599674.26871398</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.28</t>
+          <t>2493232.13727932</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.37</t>
+          <t>2482452.61111557</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.26</t>
+          <t>2478862.25979682</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>57.34</t>
+          <t>2486717.34075303</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>56.68</t>
+          <t>2420950.72117064</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56.35</t>
+          <t>2383741.30215885</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>56.76</t>
+          <t>2260411.86971817</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>55.79</t>
+          <t>2211939.44893942</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>2138756.83350249</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>2059858.57078666</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>55.87</t>
+          <t>1908639.02639897</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55.02</t>
+          <t>1836101.17707021</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>54.94</t>
+          <t>1810276.35294746</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>1300626.89422955</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>1317345.60765021</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>1321978.39610545</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>1349343.23876183</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>1404855.31605717</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>1447874.67264405</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>1381721.17149305</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>1375851.17356572</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>1455302.49922254</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>8.24</t>
+          <t>1621614.36025288</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1743484.30093618</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>1866789.31420579</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>2112509.45668382</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2285142.77605003</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>2021499.07589168</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>3005104.24557771</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>3029728.67482594</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>41.66</t>
+          <t>3015064.70670337</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>3046085.17708483</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>3232344.53931518</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>3435034.14423214</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>43.56</t>
+          <t>3200234.23955804</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43.98</t>
+          <t>3136281.67615818</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>3380988.77803731</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>3876669.44267631</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>4263810.92140011</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>4553265.30908434</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>45.37</t>
+          <t>5006497.10582246</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>45.94</t>
+          <t>5486820.8693764</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>4400016.37590637</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>53.65</t>
+          <t>1.51151547617612</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.93</t>
+          <t>1.54173376687754</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>53.38</t>
+          <t>1.55172542431666</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>53.08</t>
+          <t>1.44065955246056</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>52.78</t>
+          <t>1.37700603575676</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>1.17270234823482</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>51.97</t>
+          <t>1.06509403855577</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>1.00139595167037</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>51.88</t>
+          <t>0.951978471197756</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>50.96</t>
+          <t>0.925122895635491</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>0.929617298455002</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>50.32</t>
+          <t>0.970385447208431</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>1.08402022109955</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>1.17275018054031</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>49.36</t>
+          <t>1.19132455776522</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>1399827.26803539</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.74</t>
+          <t>1443082.12201214</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1499854.86951382</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>1523889.99594355</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>1607511.00123559</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>1706741.1994334</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>1747700.9362169</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4.62</t>
+          <t>1735706.62610792</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>1752771.61836829</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>1815309.71499575</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1899793.23249477</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>1999850.73103332</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2111579.01048659</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>2255094.07155205</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2307970.69815729</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.0000000020846</t>
+          <t>2351.13033528636</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.999999998842423</t>
+          <t>2341.12139715746</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.999999995079282</t>
+          <t>2352.77658737099</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.99999999562278</t>
+          <t>2478.57604895502</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.999999996660455</t>
+          <t>2549.0050763773</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.00000000300325</t>
+          <t>2797.36817680217</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.9999999982869</t>
+          <t>2928.85532131472</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.999999996719295</t>
+          <t>3017.42829659272</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.999999999213553</t>
+          <t>3107.21637305638</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.00000000130348</t>
+          <t>3178.43825506002</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.000000002288</t>
+          <t>3173.99845339801</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.999999996442966</t>
+          <t>3138.68291340135</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.00000000279833</t>
+          <t>2988.76685939412</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.00000000415777</t>
+          <t>2884.40273203115</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.999999995453474</t>
+          <t>2874.70085239688</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>204429247295.593</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>211979672369.517</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>222672723407.986</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4.908</t>
+          <t>236661047605.762</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>5.214</t>
+          <t>242393347034.986</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.636</t>
+          <t>266996360266.975</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5.846</t>
+          <t>274682886531.422</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.991</t>
+          <t>279169009928.013</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>291545574902.267</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>6.575</t>
+          <t>314669108188.572</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>6.954</t>
+          <t>319783781043.492</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>7.354</t>
+          <t>328445529669.115</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>7.764</t>
+          <t>317027482906.959</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>289277358227.136</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>7.756</t>
+          <t>288187301321.166</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>169610174656.741</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.688</t>
+          <t>175471720305.582</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.974</t>
+          <t>186225656405.041</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5.309</t>
+          <t>200822288738.466</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>5.622</t>
+          <t>204819855117.909</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6.081</t>
+          <t>226994846872.811</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>6.309</t>
+          <t>236408720546.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>241644126556.069</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6.766</t>
+          <t>255955635693.959</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7.112</t>
+          <t>276134018156.001</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>7.476</t>
+          <t>278461483881.761</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>7.914</t>
+          <t>285184746625.586</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>8.333</t>
+          <t>269556514375.185</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>8.529</t>
+          <t>250267345042.802</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>8.31</t>
+          <t>250902813671.046</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18.821</t>
+          <t>34819072638.852</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.468</t>
+          <t>36507952063.9344</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>36447067002.9458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>20.583</t>
+          <t>35838758867.2967</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21.128</t>
+          <t>37573491917.0762</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>22.081</t>
+          <t>40001513394.1645</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>23.016</t>
+          <t>38274165985.3327</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23.567</t>
+          <t>37524883371.9438</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>24.422</t>
+          <t>35589939208.3085</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26.072</t>
+          <t>38535090032.5708</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>27.759</t>
+          <t>41322297161.7311</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>28.717</t>
+          <t>43260783043.5286</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>28.562</t>
+          <t>47470968531.7734</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>29.835</t>
+          <t>39010013184.3341</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>29.951</t>
+          <t>37284487650.1207</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>13.475</t>
+          <t>5904.90022357886</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14.273</t>
+          <t>5950.50730751463</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>15.168</t>
+          <t>6003.63983573155</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>15.986</t>
+          <t>6049.36031038203</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>17.016</t>
+          <t>6059.00045172347</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>18.305</t>
+          <t>6077.84840661543</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>18.576</t>
+          <t>6048.36166383939</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>18.873</t>
+          <t>6039.06877725628</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19.828</t>
+          <t>6065.21946555922</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>21.265</t>
+          <t>6118.88425717975</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>23.072</t>
+          <t>6124.60232094622</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>6184.41513596778</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>25.795</t>
+          <t>6228.65057112954</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>26.565</t>
+          <t>6267.08655677164</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>24.803</t>
+          <t>6299.40257408589</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7.421</t>
+          <t>5938.56828855467</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>7.845</t>
+          <t>5986.98552232009</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.336</t>
+          <t>6036.4037128453</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>8.791</t>
+          <t>6086.43511869547</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>9.351</t>
+          <t>6097.65589542157</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>6123.6740945169</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10.284</t>
+          <t>6101.19496463609</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>10.641</t>
+          <t>6089.93219167039</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>11.138</t>
+          <t>6111.59240423576</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>11.866</t>
+          <t>6167.72956163143</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>12.637</t>
+          <t>6170.06677866516</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>13.396</t>
+          <t>6237.24523895607</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>6282.5259252136</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>14.368</t>
+          <t>6298.59993558622</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>14.117</t>
+          <t>6335.9297968304</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>227.84</t>
+          <t>765225.323280749</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>230.7</t>
+          <t>816263.572723101</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>227.73</t>
+          <t>902571.294436322</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>208.94</t>
+          <t>864155.90461674</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>202.03</t>
+          <t>889289.080588457</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>165.45</t>
+          <t>982508.583328981</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>150.94</t>
+          <t>924669.562171277</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>144.85</t>
+          <t>903145.931181632</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>137.74</t>
+          <t>945047.328505496</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>129.83</t>
+          <t>1073132.50756792</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>130.28</t>
+          <t>1187011.26399842</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>132.13</t>
+          <t>1348900.28791161</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>149.63</t>
+          <t>1530925.40769045</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>157.81</t>
+          <t>1641838.63600932</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>157.93</t>
+          <t>1402113.67875685</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>116.81</t>
+          <t>58295118560.9766</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>118.64</t>
+          <t>59412816824.954</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>122.3</t>
+          <t>62858429030.9089</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>111.28</t>
+          <t>59040083275.514</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>104.32</t>
+          <t>59137064987.6357</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>91.27</t>
+          <t>66426714800.5079</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>82.28</t>
+          <t>61363293902.9002</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>56284707280.1074</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>70.77</t>
+          <t>56327558922.8652</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>63615062831.2588</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>69.53</t>
+          <t>66523530972.3901</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>74.54</t>
+          <t>73045416666.0361</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>75375571808.2836</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>88.71</t>
+          <t>81732434521.6983</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>90.74</t>
+          <t>66218183713.0572</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>836252.814511321</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>892267.221763333</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>969989.914351957</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>987743.852605666</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>1111816.71322843</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>1316038.53269519</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>1252718.02737742</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>1281712.50205058</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1391176.22539431</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1624997.12064493</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>1834853.24155983</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>2032551.14878045</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>2161402.76732619</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>2337644.78531994</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>1779776.51207469</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>795645.348</t>
+          <t>283150269873.768</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>814367.288</t>
+          <t>292784427610.783</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>836330.654</t>
+          <t>303180369570.073</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>863588.546</t>
+          <t>330133221563.671</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>881321.118</t>
+          <t>365914352518.168</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>904568.794</t>
+          <t>432022910913.759</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>895764.201</t>
+          <t>438788075676.46</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>885470.276</t>
+          <t>453809198555.873</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>887336.21</t>
+          <t>479968570350.098</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>905823.592</t>
+          <t>529785842781.907</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>918743.492</t>
+          <t>551948888427.423</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>943816.155</t>
+          <t>562136291841.234</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>958507.06</t>
+          <t>523931296708.668</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>955767.132</t>
+          <t>502296883284.086</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>920894.631</t>
+          <t>433870201177.022</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>729360.132</t>
+          <t>-71027.4912305726</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>747143.006</t>
+          <t>-76003.6490402315</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>768803.268</t>
+          <t>-67418.619915635</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>796112.628</t>
+          <t>-123587.947988926</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>814732.484</t>
+          <t>-222527.632639969</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>835936.668</t>
+          <t>-333529.949366208</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>827065.706</t>
+          <t>-328048.465206144</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>818209.817</t>
+          <t>-378566.570868951</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>818504.646</t>
+          <t>-446128.896888809</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>835202.794</t>
+          <t>-551864.613077001</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>852211.727</t>
+          <t>-647841.977561411</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>874884.567</t>
+          <t>-683650.860868848</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>889685.078</t>
+          <t>-630477.359635741</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>891913.841</t>
+          <t>-695806.149310616</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>857821.762</t>
+          <t>-377662.833317842</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>688904.487</t>
+          <t>-224855151312.792</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>696677.023</t>
+          <t>-233371610785.829</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>704925.972</t>
+          <t>-240321940539.164</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>721066.183</t>
+          <t>-271093138288.157</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>741618.571</t>
+          <t>-306777287530.533</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>783652.956</t>
+          <t>-365596196113.251</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>756836.35</t>
+          <t>-377424781773.56</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>732297.768</t>
+          <t>-397524491275.765</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>737335.527</t>
+          <t>-423641011427.233</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>779488.088</t>
+          <t>-466170779950.648</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>806016.86</t>
+          <t>-485425357455.033</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>827003.985</t>
+          <t>-489090875175.198</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>811145.798</t>
+          <t>-448555724900.384</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>813774.405</t>
+          <t>-420564448762.388</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>706030.255</t>
+          <t>-367652017463.964</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.005</t>
+          <t>2481581.52908</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2601500.87503</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3.015</t>
+          <t>2728773.84402</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3.046</t>
+          <t>2860237.03224</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.232</t>
+          <t>3011908.57278</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3.435</t>
+          <t>3153277.12626</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3174749.14446</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>3.136</t>
+          <t>3247880.3611</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>3.381</t>
+          <t>3413364.94667</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3.877</t>
+          <t>3709101.98696</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>4.264</t>
+          <t>3927881.71778</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4.553</t>
+          <t>4182870.69581</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>5.006</t>
+          <t>4362060.14796</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>5.487</t>
+          <t>4448510.34399</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4247382.99525</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>298161.937</t>
+          <t>0.0827483145243228</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>302919.672</t>
+          <t>0.0880419732613603</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>309080.234</t>
+          <t>0.092657334365213</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>319415.158</t>
+          <t>0.0951668600958765</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>322325.414</t>
+          <t>0.100431300522277</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>330311.496</t>
+          <t>0.0979347699306751</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>326768.833</t>
+          <t>0.0967603486554795</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>321250.719</t>
+          <t>0.103730692648302</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>317376.456</t>
+          <t>0.107222921458774</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>326060.577</t>
+          <t>0.112731366452803</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>329582.565</t>
+          <t>0.117467026742387</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>339062.65</t>
+          <t>0.121255685488929</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>342265.886</t>
+          <t>0.126571038915979</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>338919.521</t>
+          <t>0.120124084232105</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>324371.408</t>
+          <t>0.116841401590213</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1.301</t>
+          <t>4111271.34380874</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>4319358.82722058</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.322</t>
+          <t>4589681.86829822</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.349</t>
+          <t>4907901.94376541</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1.405</t>
+          <t>5214254.20605125</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>5636194.04466866</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.382</t>
+          <t>5845754.13298404</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.376</t>
+          <t>5990808.40708692</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.455</t>
+          <t>6259694.94570284</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.622</t>
+          <t>6574879.48097678</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.743</t>
+          <t>6954263.47887655</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.867</t>
+          <t>7354289.12302536</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.113</t>
+          <t>7764091.97723864</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2.285</t>
+          <t>7980292.02050788</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>7755767.15769361</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>290406.386</t>
+          <t>4464095.61405741</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>293950.144</t>
+          <t>4688432.49356206</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>301287.615</t>
+          <t>4974147.50682848</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>326187.496</t>
+          <t>5308510.72048344</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>342755.749</t>
+          <t>5622009.90984497</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>384745.14</t>
+          <t>6080751.6551146</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>400497.842</t>
+          <t>6309483.70364426</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>408819.562</t>
+          <t>6460328.12366782</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>419320.529</t>
+          <t>6766131.10358599</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>433843.884</t>
+          <t>7111650.34206001</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>441648.055</t>
+          <t>7475981.94805311</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>444016.965</t>
+          <t>7914364.89918369</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>426908.083</t>
+          <t>8333069.16370465</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>410499.95</t>
+          <t>8528874.97863706</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>391462.67</t>
+          <t>8309518.9298135</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>151.15</t>
+          <t>18820738.7267015</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>154.17</t>
+          <t>19467731.1849622</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>155.17</t>
+          <t>20100491.6054108</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>144.07</t>
+          <t>20582893.4693189</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>137.7</t>
+          <t>21128069.7648515</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>117.27</t>
+          <t>22081105.0672071</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>106.51</t>
+          <t>23016105.2719886</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>100.14</t>
+          <t>23566756.2963514</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>24422075.8107447</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>92.51</t>
+          <t>26071712.8527379</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>92.96</t>
+          <t>27759307.9911121</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>28717271.640767</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>108.4</t>
+          <t>28562155.6013977</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>117.28</t>
+          <t>29834682.0875331</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>119.13</t>
+          <t>29950773.6097914</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2.716</t>
+          <t>4464095.61405741</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4618134.06551089</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.493</t>
+          <t>4814977.98990195</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>5076899.34352241</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.479</t>
+          <t>5305516.48050572</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.487</t>
+          <t>5669643.35579082</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.421</t>
+          <t>5836610.34673127</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.384</t>
+          <t>5883198.84464637</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>6058920.49734251</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.212</t>
+          <t>6221164.41130242</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>6379285.68208567</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>6623323.4142658</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>6818904.07859186</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.836</t>
+          <t>6860087.69765911</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>6504620.82767745</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4111271.34380874</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4256259.01263842</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>4445784.69312123</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4699256.47206462</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>4929195.97370424</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5268368.89972042</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5428023.58509812</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5472332.77054786</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>5625015.66957408</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>5782075.40858483</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>5958112.24035796</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>6182964.88929049</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>6382953.28214258</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>6440763.98475052</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>6087617.53329479</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2957211.67577259</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3157059.59045794</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3362312.84110152</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3482699.33910656</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>3729430.52524503</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3869249.1440054</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3974747.30702574</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>4180302.58020218</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>4371377.93488401</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>4754409.53064999</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>5160596.60663689</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>5481983.18920631</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>5726720.71863535</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>5838957.93567294</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>5807461.0654365</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>729360131673.022</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>747143005922.891</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>768803267695.24</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>796112628242.348</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>814732484437.233</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>835936668353.144</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>827065705881.27</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>818209817259.862</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>818504645986.804</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>835202794097.534</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>852211726666.561</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>874884567037.148</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>889685077707.705</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>891913840629.426</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>857821762169.447</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>795645347744.743</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>814367288232.58</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>836330653709.28</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>863588546011.44</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>881321117528.403</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>904568794010.581</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>895764201085.918</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>885470275602.398</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>887336210092.949</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>905823592446.395</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>918743492282.992</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>943816154649.907</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>958507059808.422</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>955767131948.07</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>920894631140.938</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>298161937232.312</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>302919672135.171</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>309080234079.365</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>319415158408.207</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>322325413947.204</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>330311496118.307</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>326768833063.63</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>321250718930.193</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>317376455817.311</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>326060577365.376</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>329582565444.648</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>339062649832.87</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>342265886079.758</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>338919521350.222</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>324371408038.222</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>133979321.123271</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>136022925.92767</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>138547833.030053</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141887415.074678</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>144534413.329251</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>147716677.936947</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>146817829.339657</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>145399036.924174</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>145189036.081327</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>146864998.439847</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>148903330.424206</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>151319391.572917</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>152567147.548354</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>151742790.734829</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>145344828.726105</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>123517774.061721</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>125559547.667366</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>128056194.03076</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>131602779.036991</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>134466483.527903</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>137538255.716162</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>136742105.02754</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>135486090.229891</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>134950540.641539</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>136495929.485433</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>139145642.771284</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>141466015.427866</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>142837532.391284</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>142317140.915456</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>136175097.889172</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>242776092779.119</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>246938593291.553</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>253228388684.215</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>258805730809.544</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>263627013743.852</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>269026187370.179</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>266094819734.222</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>262808915243.401</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>261841125587.143</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>264757460055.455</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>267643044069.724</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>273342067665.799</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>275293944514.337</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>271688067727.256</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>259200647761.736</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>222377917711.506</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>226311857377.698</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>232419815564.116</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>238264032694.127</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>243345873747.246</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>248180095947.989</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>245372044378.705</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>242440735569.293</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>240823364771.45</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>243449993125.228</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>247601001874.047</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>252739809254.507</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>254926997513.093</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>252853572165.955</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>240900196848.347</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.316193820598937</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.315040474579303</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.314148865416901</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.324167870372589</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.325728184531695</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.338735173747623</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.347724687054552</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.349000421584222</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.340986203952517</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.359613721853134</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.361083830034479</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.369212977323187</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.364127458318386</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.375007521109898</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.379223506756898</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.584390359486787</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.590349649645511</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.582830657193358</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.583688997296989</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.582617935738407</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.573386304427815</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.566839573924319</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.563500494379218</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.567575384021138</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.557947784553062</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.557538159938588</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.549410554976046</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.558717571172456</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.55023438139401</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.549429508172603</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0994158199142756</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0946098757751858</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.103020477389742</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0921431323304222</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0916538797298983</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0878785218245616</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0854357390211285</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.0874990840365595</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0914384120263447</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.082438493593804</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0813780100269325</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0813764677007675</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0771549705091588</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0747580974960919</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0713469850704996</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.414075250524946</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.413238752388813</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.416583171486772</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.423052783576711</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.424751474484819</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.427653072469849</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.435575195878394</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.439834309884847</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.433232837075673</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.44628808354747</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.449205122214138</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.453646319351127</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.453651749318137</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.459440576178621</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.469778038443654</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.536539450425186</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.539328388650854</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.533761083967983</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.530822349168993</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.527792000424003</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.527012066199086</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.519733139183468</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.514008099533897</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.518776588626101</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.509619680832761</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.507878752420596</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.503183389493176</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.505864707394152</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.501108006188618</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.493573498532951</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0493852990498679</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0474328589603329</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0496557445452446</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0461248672542955</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.047456525091178</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0453348613310652</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0446916649381386</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0461575905812552</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0479905742982254</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0440922356197692</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0429161253652655</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0431702911556972</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0404835432877115</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0394514176327612</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.036648463023395</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>13475212.97756</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>14272864.33987</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>15168254.22658</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>15986187.04982</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17016289.90821</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>18304783.0254</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>18575525.02881</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18873334.93361</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>19828498.0708</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>21264711.10108</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>23072266.03663</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>24479922.10987</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>25795266.07911</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>26565031.96168</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>24802899.209</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7421307.28983</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>7845492.08402</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8336460.34793</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>8791210.05959</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>9351440.43509</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9950000.79912</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10284231.01067</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>10640630.70387</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11137509.03847</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>11866059.87271</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>12636578.55469</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>13396348.08839</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>14059789.88234</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>14367832.91431</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>14116979.99525</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>18820738.9191827</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19498613.6525624</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20283897.9383015</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>21189899.9145217</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22263534.1456492</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>23387726.465827</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>24337515.189576</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>25106423.4745591</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>25927327.1323067</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>26827138.3114804</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>27863993.3167719</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>29027701.0853574</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>30191130.2566561</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>31033568.8035416</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>31372991.962419</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
